--- a/linalg/SME_PHASE1_BENCH.xlsx
+++ b/linalg/SME_PHASE1_BENCH.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-way comparison" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SME microbench" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correctness" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2A delta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SME microbench" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correctness" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -58,7 +60,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +92,11 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -117,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,6 +167,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +567,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -873,6 +889,510 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase 2A — SME2 GEMV kernel (mmv_f32 64x1) added on top of Phase 1 (mmm_f32 32x32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M4 Air, same binary, TRACT_SME_DISABLE=1 toggles entire SME backend (mmm + mmv). 8 paired runs of 10 reps; values = min-of-10 each, reported as min/median across the 8 samples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>M4+AMX min (ms)</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Phase 1 SME min (ms)</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Phase 2A SME+SME2 min (ms)</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Phase 2A / AMX</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Phase 2A / Phase 1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>df_dec</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>7.893</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>4.346</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>DFN3 GRU mmv hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>erb_dec</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>6.514</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>3.712</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>DFN3 conv path partially mmv</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>enc</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>4.298</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>DFN3 conv path partially mmv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>squeezenet</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>12.299</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>6.586</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>MMM dominant</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>mobilenetv2</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>39.091</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>27.412</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>MMM dominant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>inception_v3</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>88.276</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>52.418</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>MMM dominant (17% stdev = thermal noise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>yolov8n</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>129.655</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>MMM dominant</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>MiniLM-L6</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>12.755</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>9.441000000000001</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>seq=128 → mostly MMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>mm 256x256x256</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>bench-overhead dominated</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>mm 16x576x1024</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>mm 768x256x100</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>mm 8x576x1024</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Microbench underlying Phase 2A (M4 Air SME2 unit, mmv-pattern K-loop):</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>ns / K-step</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>GFLOPS</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>FMOPA depth-4 (mmm 32x32 reference)</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C22" s="29" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>98% arch peak, Phase 1 path</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SME2 multi-vec vgx4 FMLA-into-ZA (mmv 64x1)</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ZA-write-port-bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SME2 multi-vec vgx2 FMLA-into-ZA</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="C24" s="29" t="n">
+        <v>124</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>same ceiling as vgx4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Plain SME predicated FMLA into Z-regs</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>matches Hello-SME paper; too slow, NOT used</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -901,7 +1421,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1007,7 +1526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1037,7 +1556,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1139,7 +1657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/linalg/SME_PHASE1_BENCH.xlsx
+++ b/linalg/SME_PHASE1_BENCH.xlsx
@@ -967,7 +967,7 @@
         <v>7.893</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>5.78</v>
+        <v>5.827</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>4.346</v>
@@ -976,7 +976,7 @@
         <v>1.82</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1.33</v>
+        <v>1.341</v>
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>6.514</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>3.712</v>
@@ -1003,7 +1003,7 @@
         <v>1.75</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1.37</v>
+        <v>1.393</v>
       </c>
       <c r="G6" s="26" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>1.36</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1.16</v>
+        <v>1.163</v>
       </c>
       <c r="G7" s="26" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>12.299</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>6.59</v>
+        <v>6.975</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>6.586</v>
@@ -1057,7 +1057,7 @@
         <v>1.87</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="G8" s="26" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>39.091</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>27.41</v>
+        <v>27.832</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>27.412</v>
@@ -1084,7 +1084,7 @@
         <v>1.43</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1</v>
+        <v>1.015</v>
       </c>
       <c r="G9" s="26" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>88.276</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>52.42</v>
+        <v>53.672</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>52.418</v>
@@ -1111,7 +1111,7 @@
         <v>1.68</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>1.024</v>
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129.655</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>92.15000000000001</v>
+        <v>93.336</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>92.15000000000001</v>
@@ -1138,7 +1138,7 @@
         <v>1.41</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1</v>
+        <v>1.013</v>
       </c>
       <c r="G11" s="26" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>12.755</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>9.44</v>
+        <v>9.429</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>9.441000000000001</v>
@@ -1165,7 +1165,7 @@
         <v>1.35</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="G12" s="26" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0.97</v>
+        <v>0.966</v>
       </c>
       <c r="G13" s="26" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>0.122</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0.08599999999999999</v>
@@ -1219,7 +1219,7 @@
         <v>1.42</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1</v>
+        <v>0.988</v>
       </c>
       <c r="G14" s="26" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>0.186</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0.046</v>
@@ -1246,7 +1246,7 @@
         <v>4.04</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>1</v>
+        <v>0.978</v>
       </c>
       <c r="G15" s="26" t="inlineStr">
         <is>
